--- a/MXG.xlsx
+++ b/MXG.xlsx
@@ -198,20 +198,10 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6034B925-50E7-A3CC-FAE6-8C775CCD7564}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23139400" y="63500"/>
-          <a:ext cx="0" cy="8267700"/>
-        </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
@@ -238,33 +228,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CEFFD1E-95F6-BC41-B05B-5DB09CB2C836}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="31394400" y="63500"/>
-          <a:ext cx="0" cy="8267700"/>
-        </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
